--- a/technology_surveys/005_donor_data_protection_awareness_survey--technology_surveys.xlsx
+++ b/technology_surveys/005_donor_data_protection_awareness_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -945,8 +945,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -974,12 +974,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'decline'}</t>
+          <t>decline</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'decline'}</t>
+          <t>decline</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'fundraising'}</t>
+          <t>fundraising</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'fundraising'}</t>
+          <t>fundraising</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'research'}</t>
+          <t>research</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'research'}</t>
+          <t>research</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'very_secure'}</t>
+          <t>very_secure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'very_secure'}</t>
+          <t>very secure</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_secure'}</t>
+          <t>somewhat_secure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_secure'}</t>
+          <t>somewhat secure</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'not_secure_at_all'}</t>
+          <t>not_secure_at_all</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'not_secure_at_all'}</t>
+          <t>not secure at all</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'complete_control'}</t>
+          <t>complete_control</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'complete_control'}</t>
+          <t>complete control</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'limited_control'}</t>
+          <t>limited_control</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'limited_control'}</t>
+          <t>limited control</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'no_control'}</t>
+          <t>no_control</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'no_control'}</t>
+          <t>no control</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'indefinite'}</t>
+          <t>indefinite</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'indefinite'}</t>
+          <t>indefinite</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'finite'}</t>
+          <t>finite</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'finite'}</t>
+          <t>finite</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'never'}</t>
+          <t>never</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'on_request'}</t>
+          <t>on_request</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'on_request'}</t>
+          <t>on request</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'1_year'}</t>
+          <t>1_year</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': '1_year'}</t>
+          <t>1 year</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'you'}</t>
+          <t>you</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'you'}</t>
+          <t>you</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'third_party'}</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'third_party'}</t>
+          <t>third party</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'gdpr'}</t>
+          <t>gdpr</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'GDPR'}</t>
+          <t>GDPR</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'ccpa'}</t>
+          <t>ccpa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'CCPA'}</t>
+          <t>CCPA</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'hipaa'}</t>
+          <t>hipaa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'HIPAA'}</t>
+          <t>HIPAA</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
